--- a/data/fmsForecastOutput/File1/RPT_RPT2771077013843XC_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT2771077013843XC_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>428.7652043595863</v>
+        <v>885.2525655502085</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>462.8841290529319</v>
+        <v>969.4177801733249</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>496.7577484073837</v>
+        <v>1051.06774887122</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>527.4010015253159</v>
+        <v>1130.21955662756</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>570.2385414205852</v>
+        <v>1230.41487998534</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>27.85896398517191</v>
+        <v>57.51917154350328</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>32.55907556260071</v>
+        <v>68.18844020634502</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>37.73119500119178</v>
+        <v>79.83376669869413</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>43.7462700368311</v>
+        <v>93.74819119065215</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>50.66957115032589</v>
+        <v>109.3307270156157</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>6954726.807827572</v>
+        <v>14359117.03358938</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>8321350.402369339</v>
+        <v>17427396.03454156</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>9788535.20997492</v>
+        <v>20711128.71591816</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>11425440.70333797</v>
+        <v>24484702.32072791</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>13396108.17672268</v>
+        <v>28905045.23505338</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>439.6693572641631</v>
+        <v>907.7658880768025</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>474.655978235129</v>
+        <v>994.0715524382966</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>509.391055378405</v>
+        <v>1077.798004335582</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>540.8136131462812</v>
+        <v>1158.962763249509</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>584.7405769974231</v>
+        <v>1261.706206452622</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>34.17669179860263</v>
+        <v>70.56310490941381</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>39.89772585879204</v>
+        <v>83.55776836662977</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>46.18121951526273</v>
+        <v>97.71279983383018</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>53.46506938446585</v>
+        <v>114.5755636413446</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>61.85000092553748</v>
+        <v>133.4549595267696</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>6954726.807827572</v>
+        <v>14359117.03358938</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>8321350.402369339</v>
+        <v>17427396.03454156</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>9788535.20997492</v>
+        <v>20711128.71591816</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>11425440.70333797</v>
+        <v>24484702.32072791</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>13396108.17672268</v>
+        <v>28905045.23505338</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -1980,34 +1980,34 @@
         </is>
       </c>
       <c r="AS8" s="154" t="n">
-        <v>0.985</v>
+        <v>1.985</v>
       </c>
       <c r="AT8" s="154" t="n">
-        <v>0.98</v>
+        <v>1.98</v>
       </c>
       <c r="AU8" s="154" t="n">
-        <v>0.975</v>
+        <v>1.975</v>
       </c>
       <c r="AV8" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AW8" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="AX8" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AY8" s="154" t="n">
-        <v>0.9675</v>
+        <v>1.9675</v>
       </c>
       <c r="AZ8" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="BA8" s="154" t="n">
-        <v>0.9625</v>
+        <v>1.9625</v>
       </c>
       <c r="BB8" s="154" t="n">
-        <v>0.96</v>
+        <v>1.96</v>
       </c>
       <c r="BD8" s="31" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>908.725553530213</v>
+        <v>1876.131095049497</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>993.5789811444811</v>
+        <v>2080.324117549972</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1070.702405156693</v>
+        <v>2264.678752641493</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1140.897112757511</v>
+        <v>2444.120628260733</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1245.560736676659</v>
+        <v>2687.01995261204</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>12.43109538979109</v>
+        <v>25.66491556852439</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>15.13348122189636</v>
+        <v>31.68600238718475</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>18.14246770335222</v>
+        <v>38.37374505780942</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>21.63402622883795</v>
+        <v>46.3461333953564</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>25.94072046430786</v>
+        <v>55.96132843646409</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>3105173.813214872</v>
+        <v>6410860.929214695</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>3875530.556646597</v>
+        <v>8114462.803960421</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>4716201.157766602</v>
+        <v>9975396.061255846</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>5646648.175497905</v>
+        <v>12096699.28334596</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>6803728.52456255</v>
+        <v>14677529.37238025</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>994.8598535110533</v>
+        <v>2053.961725999178</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1087.756183143579</v>
+        <v>2277.509352302446</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1172.189814416509</v>
+        <v>2479.33819330811</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1249.037985186783</v>
+        <v>2675.788614888965</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1363.622236895819</v>
+        <v>2941.711351740935</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>12.86351186086133</v>
+        <v>26.5576713452656</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>15.66125059862226</v>
+        <v>32.79102914775745</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>18.77696095277867</v>
+        <v>39.71578311969294</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>22.39314037523445</v>
+        <v>47.97236815716403</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>26.85373433006303</v>
+        <v>57.93095256000652</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>3105173.813214872</v>
+        <v>6410860.929214695</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>3875530.556646597</v>
+        <v>8114462.803960421</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>4716201.157766602</v>
+        <v>9975396.061255846</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>5646648.175497905</v>
+        <v>12096699.28334596</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>6803728.52456255</v>
+        <v>14677529.37238025</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2128,34 +2128,34 @@
         </is>
       </c>
       <c r="AS9" s="154" t="n">
-        <v>0.98222200886944</v>
+        <v>1.98222200886944</v>
       </c>
       <c r="AT9" s="154" t="n">
-        <v>0.959877939943838</v>
+        <v>1.95987793994383</v>
       </c>
       <c r="AU9" s="154" t="n">
-        <v>0.953844334714395</v>
+        <v>1.95384433471439</v>
       </c>
       <c r="AV9" s="154" t="n">
-        <v>0.942019789921236</v>
+        <v>1.94201978992123</v>
       </c>
       <c r="AW9" s="154" t="n">
-        <v>0.9396716375637419</v>
+        <v>1.93967163756374</v>
       </c>
       <c r="AX9" s="154" t="n">
-        <v>0.959183430955845</v>
+        <v>1.95918343095584</v>
       </c>
       <c r="AY9" s="154" t="n">
-        <v>0.958736584295856</v>
+        <v>1.95873658429585</v>
       </c>
       <c r="AZ9" s="154" t="n">
-        <v>0.957337586100609</v>
+        <v>1.9573375861006</v>
       </c>
       <c r="BA9" s="154" t="n">
-        <v>0.95373489701852</v>
+        <v>1.95373489701852</v>
       </c>
       <c r="BB9" s="154" t="n">
-        <v>0.951703088585464</v>
+        <v>1.95170308858546</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>512.2820270682089</v>
+        <v>1057.67311365793</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>557.5015061140462</v>
+        <v>1167.480835409096</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>601.6161419840165</v>
+        <v>1272.791740524059</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>641.4949598732546</v>
+        <v>1374.570207586275</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>697.6407914031304</v>
+        <v>1505.209289072195</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>20.14270816918894</v>
+        <v>41.58725026668261</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>23.83754563762309</v>
+        <v>49.91892827177687</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>27.92692168446683</v>
+        <v>59.08278182335736</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>32.69369380069365</v>
+        <v>70.05476314772714</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>38.35449105650171</v>
+        <v>82.75252383073845</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>10059900.62104245</v>
+        <v>20769977.96280408</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>12196880.95901594</v>
+        <v>25541858.83850198</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>14504736.36774152</v>
+        <v>30686524.77717401</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>17072088.87883588</v>
+        <v>36581401.60407387</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>20199836.70128523</v>
+        <v>43582574.60743363</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>531.1653512635377</v>
+        <v>1096.660201321707</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>578.2102640126876</v>
+        <v>1210.847674254631</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>624.1398513814325</v>
+        <v>1320.443372995977</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>665.6514271798303</v>
+        <v>1426.331737071575</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>724.0359344107221</v>
+        <v>1562.158674674359</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>22.61224950069322</v>
+        <v>46.68594069770824</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>26.74596966688686</v>
+        <v>56.00954736099983</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>31.31901277604872</v>
+        <v>66.25916095147156</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>36.64648059641988</v>
+        <v>78.52463946198411</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>42.9826981130621</v>
+        <v>92.73820749363463</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>10059900.62104245</v>
+        <v>20769977.96280408</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>12196880.95901594</v>
+        <v>25541858.83850198</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>14504736.36774152</v>
+        <v>30686524.77717401</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>17072088.87883588</v>
+        <v>36581401.60407387</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>20199836.70128523</v>
+        <v>43582574.60743363</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2276,34 +2276,34 @@
         </is>
       </c>
       <c r="AS10" s="154" t="n">
-        <v>0.980726167491445</v>
+        <v>1.98072616749144</v>
       </c>
       <c r="AT10" s="154" t="n">
-        <v>0.9490429845289819</v>
+        <v>1.94904298452898</v>
       </c>
       <c r="AU10" s="154" t="n">
-        <v>0.9424528226375311</v>
+        <v>1.94245282263753</v>
       </c>
       <c r="AV10" s="154" t="n">
-        <v>0.926953522955747</v>
+        <v>1.92695352295574</v>
       </c>
       <c r="AW10" s="154" t="n">
-        <v>0.926033288559604</v>
+        <v>1.9260332885596</v>
       </c>
       <c r="AX10" s="154" t="n">
-        <v>0.953359124547455</v>
+        <v>1.95335912454745</v>
       </c>
       <c r="AY10" s="154" t="n">
-        <v>0.9540178219936239</v>
+        <v>1.95401782199362</v>
       </c>
       <c r="AZ10" s="154" t="n">
-        <v>0.953211670924014</v>
+        <v>1.95321167092401</v>
       </c>
       <c r="BA10" s="154" t="n">
-        <v>0.949015226182339</v>
+        <v>1.94901522618233</v>
       </c>
       <c r="BB10" s="154" t="n">
-        <v>0.9472355209007139</v>
+        <v>1.94723552090071</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1154.980030706727</v>
+        <v>2358.682825752265</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1257.46452441102</v>
+        <v>2601.679515095991</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1341.362916536731</v>
+        <v>2807.091642776165</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1408.858678459484</v>
+        <v>2990.349814763193</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1490.351452081349</v>
+        <v>3190.328784206696</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>29.04582988532735</v>
+        <v>59.3169563878283</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>35.19968805467656</v>
+        <v>72.82774628772538</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>42.69992522632329</v>
+        <v>89.35881689606632</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>51.41590907964218</v>
+        <v>109.1319921174129</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>62.32076619597447</v>
+        <v>133.4072805251177</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>113934.0386528224</v>
+        <v>232674.3779929854</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>141226.382747472</v>
+        <v>292195.7477546345</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>173451.5093828409</v>
+        <v>362984.7496251035</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>209926.156542169</v>
+        <v>445575.3106594339</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>256112.9973290932</v>
+        <v>548249.6536285854</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1246.044638901905</v>
+        <v>2544.653597257636</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1356.609540939798</v>
+        <v>2806.809404265302</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1447.122916878222</v>
+        <v>3028.417288087066</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1519.940394286021</v>
+        <v>3226.124483595611</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1607.858480297116</v>
+        <v>3441.870830842611</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>29.5220467021243</v>
+        <v>60.28947919969551</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>35.78284291459333</v>
+        <v>74.03428692861127</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>43.41724002015322</v>
+        <v>90.85995304510982</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>52.29412392064806</v>
+        <v>110.9960325831293</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>63.40529101218925</v>
+        <v>135.7288743569111</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>113934.0386528224</v>
+        <v>232674.3779929854</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>141226.382747472</v>
+        <v>292195.7477546345</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>173451.5093828409</v>
+        <v>362984.7496251035</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>209926.156542169</v>
+        <v>445575.3106594339</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>256112.9973290932</v>
+        <v>548249.6536285854</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="AS11" s="154" t="n">
-        <v>0.985</v>
+        <v>1.985</v>
       </c>
       <c r="AT11" s="154" t="n">
-        <v>0.98</v>
+        <v>1.98</v>
       </c>
       <c r="AU11" s="154" t="n">
-        <v>0.975</v>
+        <v>1.975</v>
       </c>
       <c r="AV11" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AW11" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="AX11" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AY11" s="154" t="n">
-        <v>0.968</v>
+        <v>1.968</v>
       </c>
       <c r="AZ11" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="BA11" s="154" t="n">
-        <v>0.963</v>
+        <v>1.963</v>
       </c>
       <c r="BB11" s="154" t="n">
-        <v>0.96</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" thickTop="1">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>515.494394687195</v>
+        <v>1064.175890152423</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>561.0764454942714</v>
+        <v>1174.805755733535</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>605.5625449721535</v>
+        <v>1280.976927573516</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>645.7674607822191</v>
+        <v>1383.56648884527</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>702.3178377590541</v>
+        <v>1515.151607732665</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>20.21208884673394</v>
+        <v>41.7254151781124</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>23.92594677188195</v>
+        <v>50.09716626799315</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>28.04156522239055</v>
+        <v>59.31773416498539</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>32.83894545722222</v>
+        <v>70.35793412166501</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>38.54005434105278</v>
+        <v>83.14472758270422</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>10173834.65969527</v>
+        <v>21002652.34079707</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>12338107.34176341</v>
+        <v>25834054.58625662</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>14678187.87712436</v>
+        <v>31049509.52679912</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>17282015.03537805</v>
+        <v>37026976.9147333</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>20455949.69861433</v>
+        <v>44130824.26106222</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>534.6001158672607</v>
+        <v>1103.617342966159</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>582.0328950230431</v>
+        <v>1218.685262214068</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>628.362660872438</v>
+        <v>1329.207160200618</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>670.2272849865595</v>
+        <v>1435.972029767353</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>729.0534484421623</v>
+        <v>1572.829914237708</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>22.67167478364848</v>
+        <v>46.80293315075824</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>26.82350974660265</v>
+        <v>56.16420702088649</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>31.42248067595709</v>
+        <v>66.46955477551316</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>36.78016535612091</v>
+        <v>78.80205698081497</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>43.15673686148605</v>
+        <v>93.10456850821056</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>10173834.65969527</v>
+        <v>21002652.34079707</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>12338107.34176341</v>
+        <v>25834054.58625662</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>14678187.87712436</v>
+        <v>31049509.52679912</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>17282015.03537805</v>
+        <v>37026976.9147333</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>20455949.69861433</v>
+        <v>44130824.26106222</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="AS12" s="154" t="n">
-        <v>0.9822</v>
+        <v>1.9822</v>
       </c>
       <c r="AT12" s="154" t="n">
-        <v>0.9599</v>
+        <v>1.9599</v>
       </c>
       <c r="AU12" s="154" t="n">
-        <v>0.9538</v>
+        <v>1.9538</v>
       </c>
       <c r="AV12" s="154" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.942</v>
       </c>
       <c r="AW12" s="154" t="n">
-        <v>0.9397</v>
+        <v>1.9397</v>
       </c>
       <c r="AX12" s="154" t="n">
-        <v>0.9592000000000001</v>
+        <v>1.9592</v>
       </c>
       <c r="AY12" s="154" t="n">
-        <v>0.9587</v>
+        <v>1.9587</v>
       </c>
       <c r="AZ12" s="154" t="n">
-        <v>0.9573</v>
+        <v>1.9573</v>
       </c>
       <c r="BA12" s="154" t="n">
-        <v>0.9537</v>
+        <v>1.9537</v>
       </c>
       <c r="BB12" s="154" t="n">
-        <v>0.9517</v>
+        <v>1.9517</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" thickBot="1">
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>941.0707137106635</v>
+        <v>1939.847980231178</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>972.6762582098897</v>
+        <v>2032.833678286449</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>851.4522878433247</v>
+        <v>1795.886701025836</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>879.7859300354991</v>
+        <v>1882.359725167961</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>918.1017327772665</v>
+        <v>1981.375203633166</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>814.9086220666813</v>
+        <v>1679.78752452714</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>849.1170384295576</v>
+        <v>1774.602492820363</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>744.7109307772943</v>
+        <v>1570.74738747735</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>775.5475039998212</v>
+        <v>1659.334772976987</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>817.381767598462</v>
+        <v>1764.00926869217</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>7093576.675913888</v>
+        <v>14622132.20208366</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>8359337.200900506</v>
+        <v>17470501.6666259</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8313683.433522604</v>
+        <v>17535255.61910217</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>9791972.644406565</v>
+        <v>20950567.98081962</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>11709892.5630463</v>
+        <v>25271372.36898902</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>599.0591769772506</v>
+        <v>1234.852724208309</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>619.1783786480459</v>
+        <v>1294.04480715817</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>542.0106048987542</v>
+        <v>1143.211018456685</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>560.0470054849385</v>
+        <v>1198.257316166936</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>584.4377690283069</v>
+        <v>1261.287787919148</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>522.9816767319858</v>
+        <v>1078.032643589812</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>544.70232984115</v>
+        <v>1138.394436377048</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>477.6781451960846</v>
+        <v>1007.520727322528</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>497.2493463976076</v>
+        <v>1063.897604030996</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>523.7921542433141</v>
+        <v>1130.407175178571</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>7093576.675913888</v>
+        <v>14622132.20208366</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>8359337.200900506</v>
+        <v>17470501.6666259</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8313683.433522604</v>
+        <v>17535255.61910217</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>9791972.644406565</v>
+        <v>20950567.98081962</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>11709892.5630463</v>
+        <v>25271372.36898902</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2709,34 +2709,34 @@
         </is>
       </c>
       <c r="AS13" s="154" t="n">
-        <v>0.9657</v>
+        <v>1.9657</v>
       </c>
       <c r="AT13" s="154" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.934</v>
       </c>
       <c r="AU13" s="154" t="n">
-        <v>0.9275</v>
+        <v>1.9275</v>
       </c>
       <c r="AV13" s="154" t="n">
-        <v>0.912</v>
+        <v>1.912</v>
       </c>
       <c r="AW13" s="154" t="n">
-        <v>0.911</v>
+        <v>1.911</v>
       </c>
       <c r="AX13" s="154" t="n">
-        <v>0.9384</v>
+        <v>1.9384</v>
       </c>
       <c r="AY13" s="154" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.939</v>
       </c>
       <c r="AZ13" s="154" t="n">
-        <v>0.9382</v>
+        <v>1.9382</v>
       </c>
       <c r="BA13" s="154" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.934</v>
       </c>
       <c r="BB13" s="154" t="n">
-        <v>0.9322</v>
+        <v>1.9322</v>
       </c>
     </row>
     <row r="14" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>633.1124791772465</v>
+        <v>1306.188589808259</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>676.7359147459596</v>
+        <v>1415.911439117713</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>676.1708350321176</v>
+        <v>1428.835468617582</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>714.505416502969</v>
+        <v>1530.076409628705</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>768.0330827235584</v>
+        <v>1657.136243843936</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>33.72154689645549</v>
+        <v>69.57168155029041</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>39.38441695345504</v>
+        <v>82.40267033605299</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>43.00700455683517</v>
+        <v>90.87930198421709</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>50.2401257274695</v>
+        <v>107.5866318391469</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>59.00936239108595</v>
+        <v>127.32075654557</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>17267411.33560915</v>
+        <v>35624784.54288073</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>20697444.54266391</v>
+        <v>43304556.25288251</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>22991871.31064697</v>
+        <v>48584765.14590128</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>27073987.67978461</v>
+        <v>57977544.89555293</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>32165842.26166062</v>
+        <v>69402196.63005124</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>559.3239426982652</v>
+        <v>1153.953801239966</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>596.4854696273477</v>
+        <v>1248.006173914837</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>594.1355977485341</v>
+        <v>1255.484518481325</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>625.7060015490483</v>
+        <v>1339.917053420018</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>668.8064336377181</v>
+        <v>1443.04119995308</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>37.35026978389494</v>
+        <v>77.05818132250948</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>43.54420924544761</v>
+        <v>91.10606166233865</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>47.45208672263794</v>
+        <v>100.2723292050921</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>55.30207356751716</v>
+        <v>118.426531436739</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>64.80501651495629</v>
+        <v>139.825671661194</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>17267411.33560915</v>
+        <v>35624784.54288073</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>20697444.54266391</v>
+        <v>43304556.25288251</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>22991871.31064697</v>
+        <v>48584765.14590128</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>27073987.67978461</v>
+        <v>57977544.89555293</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>32165842.26166062</v>
+        <v>69402196.63005124</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="T20" s="79" t="n">
-        <v>3121.217327502071</v>
+        <v>3121.21732750207</v>
       </c>
       <c r="U20" s="80" t="n">
         <v>3562.8669518995</v>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97097200886944</v>
+        <v>1.97097200886944</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.948627939943838</v>
+        <v>1.94862793994383</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.942594334714395</v>
+        <v>1.94259433471439</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.930769789921236</v>
+        <v>1.93076978992123</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.928421637563742</v>
+        <v>1.92842163756374</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.947933430955845</v>
+        <v>1.94793343095584</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.947486584295856</v>
+        <v>1.94748658429585</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.9460875861006091</v>
+        <v>1.9460875861006</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94248489701852</v>
+        <v>1.94248489701852</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.9404530885854641</v>
+        <v>1.94045308858546</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.97095</v>
+        <v>1.97095</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.94865</v>
+        <v>1.94865</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.94255</v>
+        <v>1.94255</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.93075</v>
+        <v>1.93075</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.92845</v>
+        <v>1.92845</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9479500000000001</v>
+        <v>1.94795</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.94745</v>
+        <v>1.94745</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9460500000000001</v>
+        <v>1.94605</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.94245</v>
+        <v>1.94245</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.94045</v>
+        <v>1.94045</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -3966,7 +3966,7 @@
         <v>500604.5449603763</v>
       </c>
       <c r="K25" s="92" t="n">
-        <v>500999.7904432034</v>
+        <v>500999.7904432033</v>
       </c>
       <c r="L25" s="93" t="n">
         <v>503216.4655729852</v>
@@ -3975,7 +3975,7 @@
         <v>512058.6961395936</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>525523.7005825018</v>
+        <v>525523.7005825017</v>
       </c>
       <c r="O25" s="92" t="n">
         <v>534607.5958455198</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>30871.93309177592</v>
+        <v>30871.93309177591</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>34698.99200661933</v>
@@ -4010,7 +4010,7 @@
         <v>431438.2840905022</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>440621.2607047732</v>
+        <v>440621.2607047731</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>445830.1197158463</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>440.0611871384052</v>
+        <v>447.7908101799588</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>486.316452135398</v>
+        <v>495.9889287688594</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>525.3022317924052</v>
+        <v>539.4859470075082</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>564.8161694201507</v>
+        <v>583.6957263862265</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>612.3950144274173</v>
+        <v>636.3693634551339</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>28.59291901280124</v>
+        <v>29.0951502753759</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>34.20729534367263</v>
+        <v>34.88765329465856</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>39.8992889509318</v>
+        <v>40.97661190429928</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>46.84974165229455</v>
+        <v>48.41574208616753</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>54.41546037616656</v>
+        <v>56.54574427598221</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>7137951.737121799</v>
+        <v>7263329.020620789</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>8742597.446439911</v>
+        <v>8916481.281019509</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>10350999.87521792</v>
+        <v>10630487.80718559</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>12235990.51449026</v>
+        <v>12644990.98661173</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>14386452.79871498</v>
+        <v>14949660.91201036</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>451.2526141085435</v>
+        <v>459.1788132497499</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>498.6842210219058</v>
+        <v>508.602683484219</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>538.6614684989734</v>
+        <v>553.205897218549</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>579.1803058092815</v>
+        <v>598.5399986955197</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>627.9691533907013</v>
+        <v>652.5532066689677</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>35.07708977415814</v>
+        <v>35.6932147342167</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>41.91744600882546</v>
+        <v>42.75115318709271</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>48.83486519543519</v>
+        <v>50.1534581474136</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>57.25801733440023</v>
+        <v>59.17192500658876</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>66.42243457408468</v>
+        <v>69.02277355829192</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>7137951.737121799</v>
+        <v>7263329.020620789</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>8742597.446439911</v>
+        <v>8916481.281019509</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>10350999.87521792</v>
+        <v>10630487.80718559</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>12235990.51449026</v>
+        <v>12644990.98661173</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>14386452.79871498</v>
+        <v>14949660.91201036</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>933.3459519124846</v>
+        <v>949.5251525313832</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1044.503135592479</v>
+        <v>1064.843359080957</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1132.689505145462</v>
+        <v>1162.747820814809</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1222.17633809282</v>
+        <v>1262.509766527799</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1337.672959339657</v>
+        <v>1389.712551263562</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>12.76789511951774</v>
+        <v>12.98922177358042</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>15.9091213569081</v>
+        <v>16.21892902801794</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>19.19280527068601</v>
+        <v>19.7021270193081</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>23.17526677814017</v>
+        <v>23.94008109741942</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>27.85909935109129</v>
+        <v>28.94290399218533</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>3189303.302069403</v>
+        <v>3244588.673857821</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>4074164.103027857</v>
+        <v>4153502.695283317</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>4989240.268658338</v>
+        <v>5121640.329102344</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>6048923.879690218</v>
+        <v>6248546.332527784</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>7306880.669888875</v>
+        <v>7591140.799125094</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1021.813916630349</v>
+        <v>1039.526676104443</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1143.507225509997</v>
+        <v>1165.775413833213</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1240.052412727773</v>
+        <v>1272.959830602648</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1338.02132883377</v>
+        <v>1382.177794499933</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1464.465392443817</v>
+        <v>1521.437599945925</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>13.21202719134714</v>
+        <v>13.44105270763415</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>16.46394063078697</v>
+        <v>16.78455262372396</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>19.86403178633561</v>
+        <v>20.39116595257205</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>23.98846135744359</v>
+        <v>24.78011216859866</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>28.83963279579629</v>
+        <v>29.9615832033678</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>3189303.302069403</v>
+        <v>3244588.673857821</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>4074164.103027857</v>
+        <v>4153502.695283317</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>4989240.268658338</v>
+        <v>5121640.329102344</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>6048923.879690218</v>
+        <v>6248546.332527784</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>7306880.669888875</v>
+        <v>7591140.799125094</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>525.8965614889967</v>
+        <v>535.0964765530254</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>585.835337029425</v>
+        <v>597.4097620661836</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>636.2705159531399</v>
+        <v>653.3544848472835</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>687.0676757149431</v>
+        <v>709.93708212417</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>749.2216176304973</v>
+        <v>778.4905876797031</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>20.67802578567208</v>
+        <v>21.03976247469197</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>25.04903830648033</v>
+        <v>25.5439354179987</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>29.53557198541843</v>
+        <v>30.32860699241346</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>35.01630038467767</v>
+        <v>36.1818362303445</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>41.19027182305571</v>
+        <v>42.79940429325926</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>10327255.0391912</v>
+        <v>10507917.69447861</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>12816761.54946777</v>
+        <v>13069983.97630283</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>15340240.14387626</v>
+        <v>15752128.13628793</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>18284914.39418048</v>
+        <v>18893537.31913951</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>21693333.46860386</v>
+        <v>22540801.71113546</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>545.2817335994428</v>
+        <v>554.8207684637848</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>607.5965736000211</v>
+        <v>619.6009382212895</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>660.091639090247</v>
+        <v>677.8152090919294</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>712.9402528729809</v>
+        <v>736.6708415249403</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>777.5683140757585</v>
+        <v>807.9446715651109</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>23.213198261126</v>
+        <v>23.61928468192737</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>28.10527681475741</v>
+        <v>28.66055642844419</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>33.12305476452612</v>
+        <v>34.01241427921068</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>39.24989878562681</v>
+        <v>40.55635216507809</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>46.16067037253122</v>
+        <v>47.96397562533188</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>10327255.0391912</v>
+        <v>10507917.69447861</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>12816761.54946777</v>
+        <v>13069983.97630283</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>15340240.14387626</v>
+        <v>15752128.13628793</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>18284914.39418048</v>
+        <v>18893537.31913951</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>21693333.46860386</v>
+        <v>22540801.71113546</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1183.438588281387</v>
+        <v>1190.801266172999</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1318.672474944847</v>
+        <v>1328.301068689306</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1415.22764396452</v>
+        <v>1437.36570765052</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1505.103944634745</v>
+        <v>1540.566296836091</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1596.15559275095</v>
+        <v>1645.739688371382</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>29.7615153518454</v>
+        <v>29.94667447482121</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>36.91305707895652</v>
+        <v>37.18258634966809</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>45.05127868864556</v>
+        <v>45.7560049431095</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>54.92835353604726</v>
+        <v>56.22254230346032</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>66.74508846172439</v>
+        <v>68.81850465217013</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>116741.3585306655</v>
+        <v>117467.6564797114</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>148100.674054678</v>
+        <v>149182.0655683764</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>183002.9501633728</v>
+        <v>185865.621043722</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>224267.1256702033</v>
+        <v>229551.1725468662</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>274295.1620519693</v>
+        <v>282816.0591406837</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1276.747016565603</v>
+        <v>1284.690206119444</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1422.643443339115</v>
+        <v>1433.031205288649</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1526.81152202149</v>
+        <v>1550.695065319403</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1623.774135778494</v>
+        <v>1662.032523515554</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1722.004767462194</v>
+        <v>1775.498330017413</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>30.24946608900333</v>
+        <v>30.43766096232584</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>37.52459740273842</v>
+        <v>37.79859197734305</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>45.8080938004528</v>
+        <v>46.52465873063451</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>55.86656305389618</v>
+        <v>57.18285734862462</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>67.90660667171498</v>
+        <v>70.01610507761053</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>116741.3585306655</v>
+        <v>117467.6564797114</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>148100.674054678</v>
+        <v>149182.0655683764</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>183002.9501633728</v>
+        <v>185865.621043722</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>224267.1256702033</v>
+        <v>229551.1725468662</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>274295.1620519693</v>
+        <v>282816.0591406837</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>529.1831233003485</v>
+        <v>538.3738553870414</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>589.578175258221</v>
+        <v>601.1426623000681</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>640.4260984353664</v>
+        <v>657.5370299273544</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>691.6223094797048</v>
+        <v>714.5618304526517</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>754.2185851982806</v>
+        <v>783.6074158583451</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>20.74881204252306</v>
+        <v>21.10917268934539</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>25.14134420072622</v>
+        <v>25.63448787772304</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>29.65597915277644</v>
+        <v>30.44832885378133</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>35.1707831027764</v>
+        <v>36.33731707017842</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>41.38813468175927</v>
+        <v>43.00086195389138</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>10443996.39772187</v>
+        <v>10625385.35095832</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>12964862.22352245</v>
+        <v>13219166.0418712</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>15523243.09403963</v>
+        <v>15937993.75733165</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>18509181.51985068</v>
+        <v>19123088.49168638</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>21967628.63065583</v>
+        <v>22823617.77027614</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>548.7961885657969</v>
+        <v>558.327555907691</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>611.5991768031707</v>
+        <v>623.595602471144</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>664.5388666227792</v>
+        <v>682.294044071553</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>717.8189841854604</v>
+        <v>741.6273885946376</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>782.9299369249668</v>
+        <v>813.4375321852106</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>23.27371121026639</v>
+        <v>23.6779237313736</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>28.18609844954642</v>
+        <v>28.73896452220463</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>33.23154126612846</v>
+        <v>34.119422986388</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>39.39186232120259</v>
+        <v>40.69839977595944</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>46.34598648569619</v>
+        <v>48.15190107774206</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>10443996.39772187</v>
+        <v>10625385.35095832</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>12964862.22352245</v>
+        <v>13219166.0418712</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>15523243.09403963</v>
+        <v>15937993.75733165</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>18509181.51985068</v>
+        <v>19123088.49168638</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>21967628.63065583</v>
+        <v>22823617.77027614</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>912.8088058909642</v>
+        <v>928.0235240451422</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>950.0056564993655</v>
+        <v>968.4842790983054</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>883.1447112442968</v>
+        <v>904.5771119078388</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>923.1987952775477</v>
+        <v>953.4039484360927</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>965.0869980434802</v>
+        <v>1004.349878600745</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>790.4355702303156</v>
+        <v>803.6105684801986</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>829.3262868599819</v>
+        <v>845.457567091234</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>772.4302692141051</v>
+        <v>791.175821107995</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>813.8167444258336</v>
+        <v>840.4431433489178</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>859.2125340628768</v>
+        <v>894.1680967910112</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>6880544.852475076</v>
+        <v>6995229.932200406</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>8164502.380325817</v>
+        <v>8323310.653899805</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>8623132.100416467</v>
+        <v>8832400.660594316</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>10275155.62603062</v>
+        <v>10611337.4440743</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>12309164.28716042</v>
+        <v>12809941.15820553</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>581.0684404772074</v>
+        <v>590.7537025968243</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>604.7469105294224</v>
+        <v>616.5098825192166</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>562.1851112375393</v>
+        <v>575.8283753568983</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>587.6824158140732</v>
+        <v>606.9101677013698</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>614.3472688462873</v>
+        <v>639.3409155188613</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>507.2756732150859</v>
+        <v>515.7309557941196</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>532.006708388078</v>
+        <v>542.3548059148153</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>495.4580939296666</v>
+        <v>507.4820082960156</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>521.7860184787183</v>
+        <v>538.8577766793981</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>550.598021646523</v>
+        <v>572.9981414313716</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>6880544.852475076</v>
+        <v>6995229.932200406</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>8164502.380325817</v>
+        <v>8323310.653899805</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>8623132.100416467</v>
+        <v>8832400.660594316</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>10275155.62603062</v>
+        <v>10611337.4440743</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>12309164.28716042</v>
+        <v>12809941.15820553</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>635.2071569003209</v>
+        <v>646.0627600585013</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>690.8582290780603</v>
+        <v>704.3655868991516</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>710.1237849514897</v>
+        <v>728.475644776589</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>759.6429844184452</v>
+        <v>784.7166305527545</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>818.4368597095875</v>
+        <v>850.8327526331793</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>33.83311597050596</v>
+        <v>34.41131928038798</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>40.20630198110574</v>
+        <v>40.99239800582327</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>45.16653968649079</v>
+        <v>46.33378689419823</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>53.41395343363958</v>
+        <v>55.17699553960316</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>62.8819751846661</v>
+        <v>65.371009874073</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>17324541.25019694</v>
+        <v>17620615.28315873</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>21129364.60384826</v>
+        <v>21542476.69577101</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>24146375.1944561</v>
+        <v>24770394.41792597</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>28784337.1458813</v>
+        <v>29734425.93576068</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>34276792.91781625</v>
+        <v>35633558.92848167</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>561.1744881246873</v>
+        <v>570.7648831311035</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>608.9330952270179</v>
+        <v>620.8386886760709</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>623.9692657367638</v>
+        <v>640.0946184465782</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>665.2338294530988</v>
+        <v>687.1912989202169</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>712.6982542977801</v>
+        <v>740.9087338957473</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>37.47384463139883</v>
+        <v>38.11426749457135</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>44.45290198201948</v>
+        <v>45.32202567192374</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>49.83482528601728</v>
+        <v>51.12271585867254</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>58.79568053517001</v>
+        <v>60.73635808791981</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>69.05798122894048</v>
+        <v>71.79147855236994</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>17324541.25019694</v>
+        <v>17620615.28315873</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>21129364.60384826</v>
+        <v>21542476.69577101</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>24146375.1944561</v>
+        <v>24770394.41792597</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>28784337.1458813</v>
+        <v>29734425.93576068</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>34276792.91781625</v>
+        <v>35633558.92848167</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3018039097730816</v>
+        <v>0.2962970798822328</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.1903269611403116</v>
+        <v>0.1860771503121187</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.1360385649083278</v>
+        <v>0.1315630381524578</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.08863977724435797</v>
+        <v>0.08482047756308872</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.04819396746469854</v>
+        <v>0.04559280772277814</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.01960967020518993</v>
+        <v>0.01925186464158135</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.01338751864758566</v>
+        <v>0.01308858873576303</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0103327983039914</v>
+        <v>0.009992860027638042</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.007352393378324116</v>
+        <v>0.007035594368225219</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.004282361654099307</v>
+        <v>0.00405123092714378</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4895.36865553511</v>
+        <v>4806.045881488561</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3421.5416672572</v>
+        <v>3345.142061339555</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2680.61904779306</v>
+        <v>2592.429479792419</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1920.262790426054</v>
+        <v>1837.522746492852</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1132.178123236285</v>
+        <v>1071.071384991455</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3094792433726916</v>
+        <v>0.3038323664012056</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1951672659622413</v>
+        <v>0.1908093759648086</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.1394982330381034</v>
+        <v>0.1349088868127935</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.09089402193276208</v>
+        <v>0.08697759163713908</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.04941961354084921</v>
+        <v>0.0467523023405858</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.0240566610887516</v>
+        <v>0.02361771402389361</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01640499736867143</v>
+        <v>0.01603869017269588</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.0126468622758566</v>
+        <v>0.01223079371080271</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008985822603459186</v>
+        <v>0.00859864259836144</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.005227280718120403</v>
+        <v>0.004945150134585208</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4895.36865553511</v>
+        <v>4806.045881488561</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3421.5416672572</v>
+        <v>3345.142061339555</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2680.61904779306</v>
+        <v>2592.429479792419</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1920.262790426054</v>
+        <v>1837.522746492852</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1132.178123236285</v>
+        <v>1071.071384991455</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3314441535800955</v>
+        <v>0.3252734971261104</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.1490710963661512</v>
+        <v>0.1457457099346357</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.1076583928418591</v>
+        <v>0.1041609598775073</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.07067969981596617</v>
+        <v>0.06768260919528735</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.03883501500445394</v>
+        <v>0.03678860447443479</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.004534057475919486</v>
+        <v>0.004449644730290045</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.002270543842409043</v>
+        <v>0.002219893945348096</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.001824212690399621</v>
+        <v>0.001764950598248902</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>0.001340249232438894</v>
+        <v>0.001283417519593855</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.0008087989921275585</v>
+        <v>0.0007661793414342631</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>1132.566045096764</v>
+        <v>1111.480514094776</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>581.4631750908768</v>
+        <v>568.4922518199847</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>474.2107933247449</v>
+        <v>458.8053946665871</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>349.815415910682</v>
+        <v>334.9818992895781</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>212.1316862015126</v>
+        <v>200.9534101961163</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3628603606411359</v>
+        <v>0.3561048134332576</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.1632009230041208</v>
+        <v>0.1595603370810408</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.1178628822704571</v>
+        <v>0.1140339422422353</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>0.07737913337195429</v>
+        <v>0.07409796104851224</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.04251602388459308</v>
+        <v>0.04027564264714542</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.004691774963549487</v>
+        <v>0.004604425915009169</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.002349727441408275</v>
+        <v>0.002297311165269631</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.001888010551666462</v>
+        <v>0.001826675897059999</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>0.001387277101467047</v>
+        <v>0.00132845122642916</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0008372656145344924</v>
+        <v>0.0007931459156027465</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>1132.566045096764</v>
+        <v>1111.480514094776</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>581.4631750908768</v>
+        <v>568.4922518199847</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>474.2107933247449</v>
+        <v>458.8053946665871</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>349.815415910682</v>
+        <v>334.9818992895781</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>212.1316862015126</v>
+        <v>200.9534101961163</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3069615420469732</v>
+        <v>0.3013392011863567</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1829714691887038</v>
+        <v>0.1788864736236705</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1308535715168514</v>
+        <v>0.1265567402894437</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.08529968056155254</v>
+        <v>0.08163328989567036</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.04642836341778473</v>
+        <v>0.04393185934728864</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.01206959532818657</v>
+        <v>0.0118485273125249</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007823460025373345</v>
+        <v>0.007648794545292923</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006074201120722216</v>
+        <v>0.005874742926692615</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.00434728534442013</v>
+        <v>0.004160428297549867</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.002552511652728805</v>
+        <v>0.00241526029898875</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>6027.934700631873</v>
+        <v>5917.526395583337</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>4003.004842348077</v>
+        <v>3913.634313159539</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3182765092089957</v>
+        <v>0.312446922183966</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1897680640251893</v>
+        <v>0.1855313286294192</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.1357525554582396</v>
+        <v>0.1312948565759569</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.08851176962481444</v>
+        <v>0.08470731544823683</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.04818497413654177</v>
+        <v>0.04559401517927329</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0135493548653416</v>
+        <v>0.01330118341367895</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.00877800205229526</v>
+        <v>0.008582025599723314</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.00681199255161733</v>
+        <v>0.00658830754266143</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004872887994626436</v>
+        <v>0.004663439249428666</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.00286052127866046</v>
+        <v>0.002706707909198012</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>6027.934700631873</v>
+        <v>5917.526395583337</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>4003.004842348077</v>
+        <v>3913.634313159539</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.3646691069618876</v>
+        <v>0.3621577156579041</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.009170822493587152</v>
+        <v>0.009107665172549869</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>35.97311037720952</v>
+        <v>35.72537193473156</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.3934215082705491</v>
+        <v>0.3907121058676359</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.009321181423338791</v>
+        <v>0.009256988615331413</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>35.97311037720952</v>
+        <v>35.72537193473156</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3072499790918276</v>
+        <v>0.3016431875460734</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.182036974231739</v>
+        <v>0.1779728420711024</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.1301554935482725</v>
+        <v>0.1258815850671054</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.08482475197956919</v>
+        <v>0.0811787749155725</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.0461544329426365</v>
+        <v>0.04367265841451275</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.01204700563103024</v>
+        <v>0.01182716818946763</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007762590981958271</v>
+        <v>0.007589284455672672</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006027063251664862</v>
+        <v>0.005829152921139568</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.004313558010967799</v>
+        <v>0.004128150648079243</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.002532748362714864</v>
+        <v>0.002396559702775196</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>6063.907811009083</v>
+        <v>5953.251767518069</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>4003.004842348077</v>
+        <v>3913.634313159539</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3186375567136396</v>
+        <v>0.3128229611702243</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.1888361344771796</v>
+        <v>0.1846202052108427</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.1350559953421802</v>
+        <v>0.130621169364502</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.08803767094436783</v>
+        <v>0.08425359469846069</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.04791142512496705</v>
+        <v>0.04533517519835579</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.01351299194529485</v>
+        <v>0.0132664027373129</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.00870268319363437</v>
+        <v>0.008508388299422083</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006753734217624572</v>
+        <v>0.006531962234242641</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.004831256750411979</v>
+        <v>0.004623597418775809</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.002836144278852596</v>
+        <v>0.002683641687431131</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>6063.907811009083</v>
+        <v>5953.251767518069</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>4003.004842348077</v>
+        <v>3913.634313159539</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="C62" s="155" t="n">
-        <v>0.9687338816240317</v>
+        <v>0.9619261449965616</v>
       </c>
       <c r="D62" s="156" t="n">
-        <v>0.00776195025178255</v>
+        <v>0.007695095376135641</v>
       </c>
       <c r="E62" s="156" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="155" t="n">
-        <v>0.8388632024375812</v>
+        <v>0.832968126548321</v>
       </c>
       <c r="I62" s="156" t="n">
-        <v>0.006775948476794173</v>
+        <v>0.006717586186633668</v>
       </c>
       <c r="J62" s="156" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="158" t="n">
-        <v>7302.095334324174</v>
+        <v>7250.78016634283</v>
       </c>
       <c r="N62" s="159" t="n">
-        <v>66.70745681680215</v>
+        <v>66.13289519433044</v>
       </c>
       <c r="O62" s="159" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="T62" s="155" t="n">
-        <v>0.6166687724745139</v>
+        <v>0.6123351586007493</v>
       </c>
       <c r="U62" s="156" t="n">
-        <v>0.004941039458381061</v>
+        <v>0.004898481522831207</v>
       </c>
       <c r="V62" s="156" t="n">
         <v>0</v>
@@ -6909,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="155" t="n">
-        <v>0.5383549422350707</v>
+        <v>0.5345716755109947</v>
       </c>
       <c r="Z62" s="156" t="n">
-        <v>0.004346721070418811</v>
+        <v>0.004309282090882977</v>
       </c>
       <c r="AA62" s="156" t="n">
         <v>0</v>
@@ -6924,10 +6924,10 @@
         <v>0</v>
       </c>
       <c r="AD62" s="158" t="n">
-        <v>7302.095334324174</v>
+        <v>7250.78016634283</v>
       </c>
       <c r="AE62" s="159" t="n">
-        <v>66.70745681680215</v>
+        <v>66.13289519433044</v>
       </c>
       <c r="AF62" s="159" t="n">
         <v>0</v>
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.4900667056318948</v>
+        <v>0.4841280044995985</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1330657255706675</v>
+        <v>0.1301248275684322</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.09278078757621762</v>
+        <v>0.08973415017274686</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.05990928242624679</v>
+        <v>0.05733423369873381</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.03209847261822417</v>
+        <v>0.03037250250751792</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.02610248248120665</v>
+        <v>0.02578616872129307</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.007744108010074373</v>
+        <v>0.007572954757211922</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005901206540337717</v>
+        <v>0.0057074289594282</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.004212494141847574</v>
+        <v>0.004031430753332204</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002466183352691456</v>
+        <v>0.002333573966416481</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>13366.00314533326</v>
+        <v>13204.0319338609</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>4069.712299164879</v>
+        <v>3979.76720835387</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.4329499907115915</v>
+        <v>0.4277034384146929</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.1172861822149912</v>
+        <v>0.1146940293710743</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.08152432171014513</v>
+        <v>0.07884731223110104</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.05246369964004855</v>
+        <v>0.05020868042553792</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.02795148474709573</v>
+        <v>0.02644850272682482</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.02891132977072699</v>
+        <v>0.0285609779821389</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.008562042698475018</v>
+        <v>0.008372812194834725</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006511138532102181</v>
+        <v>0.00629733264934023</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.004636924322182092</v>
+        <v>0.004437617877640572</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.00270840162347226</v>
+        <v>0.00256276789486776</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>13366.00314533326</v>
+        <v>13204.0319338609</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>4069.712299164879</v>
+        <v>3979.76720835387</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>3154.829841117804</v>
+        <v>3051.234874459007</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2270.078206336736</v>
+        <v>2172.504645782431</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1344.309809437798</v>
+        <v>1272.024795187571</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>1.240915775466739</v>
+        <v>1.218273550289788</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>1.435828184104378</v>
+        <v>1.403767575729862</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>1.558843138619756</v>
+        <v>1.507558826852734</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.696084889866561</v>
+        <v>1.623004195389914</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.732744931485474</v>
+        <v>1.639223966188353</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.08062834284557915</v>
+        <v>0.0791571671780224</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.1009955524653997</v>
+        <v>0.09874042271449508</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.1184018057656886</v>
+        <v>0.114506509972141</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.1406849577132059</v>
+        <v>0.1346231417784459</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.1539661671632151</v>
+        <v>0.1456561935978286</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>20128.10303201954</v>
+        <v>19760.83794421418</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>25812.13890823187</v>
+        <v>25235.7796432397</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>30716.76485797619</v>
+        <v>29706.2153636598</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>36743.42157286882</v>
+        <v>35160.22560075877</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>40705.83950187096</v>
+        <v>38508.83442958887</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>1.272474155717303</v>
+        <v>1.249256104230477</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>1.472343484098368</v>
+        <v>1.439467525568628</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>1.598486896473541</v>
+        <v>1.545898346462772</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.739218914713262</v>
+        <v>1.664279666746632</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>1.776811277087769</v>
+        <v>1.680911931047493</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.09891286787018051</v>
+        <v>0.09710806574622312</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.1237594371337213</v>
+        <v>0.1209960125885555</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.1449182773801905</v>
+        <v>0.1401506173547654</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.171939939545805</v>
+        <v>0.1645314128468444</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.1879393759480253</v>
+        <v>0.1777957757350788</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>20128.10303201954</v>
+        <v>19760.83794421418</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>25812.13890823187</v>
+        <v>25235.7796432397</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>30716.76485797619</v>
+        <v>29706.2153636598</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>36743.42157286882</v>
+        <v>35160.22560075877</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>40705.83950187096</v>
+        <v>38508.83442958887</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>2.258930224508234</v>
+        <v>2.216874625643687</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>2.728325982645054</v>
+        <v>2.66746416285167</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>3.094889169146736</v>
+        <v>2.994347380295316</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.460659809672957</v>
+        <v>3.313914547823556</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>3.825158607543029</v>
+        <v>3.623591932402782</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.0309014938455898</v>
+        <v>0.03032618575710366</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>0.041555901251062</v>
+        <v>0.04062889773704577</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.05244120731052444</v>
+        <v>0.05073758158941925</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.06562204799571855</v>
+        <v>0.06283942122919574</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.07966481862190693</v>
+        <v>0.07546688220598852</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>7718.910238380733</v>
+        <v>7575.203545214742</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>10642.04347605476</v>
+        <v>10404.64730844392</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>13632.28457542605</v>
+        <v>13189.42080795781</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>17127.8620848452</v>
+        <v>16401.57497637655</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>20894.47745322797</v>
+        <v>19793.44327892344</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>2.473044786201486</v>
+        <v>2.427002912763279</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>2.986932607848597</v>
+        <v>2.920301950342774</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>3.388240787869402</v>
+        <v>3.278169062759564</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>3.788681299791754</v>
+        <v>3.628026667444516</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>4.187729416404355</v>
+        <v>3.967057077958807</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.03197640434225306</v>
+        <v>0.03138108412405503</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>0.04300513370332971</v>
+        <v>0.04204580160214694</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.05427522419148889</v>
+        <v>0.0525120178754357</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.06792465336478561</v>
+        <v>0.06504438729061543</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.0824687146861951</v>
+        <v>0.07812302700945239</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>7718.910238380733</v>
+        <v>7575.203545214742</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>10642.04347605476</v>
+        <v>10404.64730844392</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>13632.28457542605</v>
+        <v>13189.42080795781</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>17127.8620848452</v>
+        <v>16401.57497637655</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>20894.47745322797</v>
+        <v>19793.44327892344</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>1.418058184005969</v>
+        <v>1.392037881262309</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>1.666267109737835</v>
+        <v>1.629071544674186</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.839475282027225</v>
+        <v>1.779191740355422</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.024248889142524</v>
+        <v>1.937468544533352</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.127487192433817</v>
+        <v>2.013582969142701</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.05575743566650465</v>
+        <v>0.05473432859472424</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.07124593895665753</v>
+        <v>0.06965553790841258</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.08538813797827194</v>
+        <v>0.08258978595670088</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.1031655390887182</v>
+        <v>0.09874279192460714</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.1169637577110555</v>
+        <v>0.110701597345217</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>27847.01327040027</v>
+        <v>27336.04148942892</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>36454.18238428662</v>
+        <v>35640.42695168362</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>44349.04943340224</v>
+        <v>42895.63617161762</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>53871.28365771402</v>
+        <v>51561.80057713532</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>61600.31695509894</v>
+        <v>58302.27770851231</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.470329493561122</v>
+        <v>1.443350051541816</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>1.728161690813588</v>
+        <v>1.689584472169888</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>1.90834279372576</v>
+        <v>1.845802316311533</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.100475056407509</v>
+        <v>2.01042686608086</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.207980376581161</v>
+        <v>2.089766602730521</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.06259342270263461</v>
+        <v>0.06144488040242842</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.07993867116990834</v>
+        <v>0.07815422495043649</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.09575964778645693</v>
+        <v>0.09262139919229798</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.1156386289503236</v>
+        <v>0.1106811555268395</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.1310776847607631</v>
+        <v>0.1240598743003427</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>27847.01327040027</v>
+        <v>27336.04148942892</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>36454.18238428662</v>
+        <v>35640.42695168362</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>44349.04943340224</v>
+        <v>42895.63617161762</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>53871.28365771402</v>
+        <v>51561.80057713532</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>61600.31695509894</v>
+        <v>58302.27770851231</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>5.833340171362662</v>
+        <v>5.793167314655419</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>6.897164721655872</v>
+        <v>6.836986759307814</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>7.797752674231762</v>
+        <v>7.64259650375088</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>8.438751779830348</v>
+        <v>8.170436478350705</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>8.980844398831142</v>
+        <v>8.579830891996233</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.1466988188332314</v>
+        <v>0.1456885381955547</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.1930694997361621</v>
+        <v>0.1913849627482022</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.2482277182544587</v>
+        <v>0.2432885949223169</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.3079699198303257</v>
+        <v>0.2981778268713364</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.3755443746106623</v>
+        <v>0.3587755319554722</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>575.435061117394</v>
+        <v>571.4721737191793</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>774.6235428066417</v>
+        <v>767.8649299165401</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>1008.32664632752</v>
+        <v>988.2634168851441</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>1257.41123239574</v>
+        <v>1217.431069131483</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>1543.334610315322</v>
+        <v>1474.42148847315</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>6.293270926052238</v>
+        <v>6.249930633234531</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>7.440972914296982</v>
+        <v>7.37605020968714</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>8.412567885926213</v>
+        <v>8.245178399285519</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>9.104106681262186</v>
+        <v>8.814636011592269</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>9.688940690280432</v>
+        <v>9.256309201393877</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.1491039986751723</v>
+        <v>0.1480771541234589</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.1962680910673681</v>
+        <v>0.1945556462772222</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2523976884265096</v>
+        <v>0.2473755929061047</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.3132302324265581</v>
+        <v>0.3032708845942227</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.3820797113646162</v>
+        <v>0.3650190522394301</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>575.435061117394</v>
+        <v>571.4721737191793</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>774.6235428066417</v>
+        <v>767.8649299165401</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>1008.32664632752</v>
+        <v>988.2634168851441</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>1257.41123239574</v>
+        <v>1217.431069131483</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>1543.334610315322</v>
+        <v>1474.42148847315</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>1.440126883153282</v>
+        <v>1.414035842355635</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>1.692983009546757</v>
+        <v>1.655670065886016</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>1.871261515524443</v>
+        <v>1.810471847109402</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.059963334284017</v>
+        <v>1.972172245682847</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.167922462120489</v>
+        <v>2.052324274694715</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.05646612807599401</v>
+        <v>0.05544312095866969</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.07219376556867024</v>
+        <v>0.07060263211243921</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.08665182857064084</v>
+        <v>0.08383686343473364</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.1047544630020372</v>
+        <v>0.100290059102355</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.1189658656028283</v>
+        <v>0.1126223553207429</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>28422.44833151767</v>
+        <v>27907.5136631481</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>37228.80592709326</v>
+        <v>36408.29188160016</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>45357.37607972976</v>
+        <v>43883.89958850276</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>55128.69489010976</v>
+        <v>52779.2316462668</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>63143.65156541426</v>
+        <v>59776.69919698546</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>1.493502172927557</v>
+        <v>1.466444122292529</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>1.756216662068705</v>
+        <v>1.717510063716388</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>1.941716631660565</v>
+        <v>1.87863816335704</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.137988852886241</v>
+        <v>2.046872488974217</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.250450240602322</v>
+        <v>2.130451498372828</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.06333742651431315</v>
+        <v>0.06218993083283228</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0809368253151411</v>
+        <v>0.07915299689747043</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.09709926629285311</v>
+        <v>0.09394490643864963</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.1173267416892407</v>
+        <v>0.1123265350333748</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.1332166922206765</v>
+        <v>0.1261132978767179</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>28422.44833151767</v>
+        <v>27907.5136631481</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>37228.80592709326</v>
+        <v>36408.29188160016</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>45357.37607972976</v>
+        <v>43883.89958850276</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>55128.69489010976</v>
+        <v>52779.2316462668</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>63143.65156541426</v>
+        <v>59776.69919698546</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>56.76488184947284</v>
+        <v>56.36596902867542</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>75.40833840468092</v>
+        <v>74.75883474603185</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>20.13026823107951</v>
+        <v>19.88665876481263</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>21.77160733293182</v>
+        <v>21.40340895517289</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>23.46399005135553</v>
+        <v>22.95172781857754</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>49.1548519954837</v>
+        <v>48.80941833955898</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>65.82920518376595</v>
+        <v>65.2622080781758</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>17.60665982721788</v>
+        <v>17.39359018730971</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>19.19207292214616</v>
+        <v>18.86749926951205</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>20.88988287286306</v>
+        <v>20.43381815328629</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>427880.7490573229</v>
+        <v>424873.8350814602</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>648071.4658795753</v>
+        <v>642489.5263081721</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>196554.3811374283</v>
+        <v>194175.7487550053</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>242316.8820399614</v>
+        <v>238218.8528266675</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>299270.5413708418</v>
+        <v>292736.9128024795</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>36.13492897666691</v>
+        <v>35.88099228239841</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>48.0028296320133</v>
+        <v>47.58937385071517</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>12.81436319624908</v>
+        <v>12.65928825422876</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>13.85919355508493</v>
+        <v>13.62480881233281</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>14.93651684616032</v>
+        <v>14.61042510077543</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>31.54597487374128</v>
+        <v>31.32428686151114</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>42.22895055963846</v>
+        <v>41.86522609004196</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>11.29339756109872</v>
+        <v>11.15672881328982</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>12.30517236833838</v>
+        <v>12.09706901451696</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>13.38659263714172</v>
+        <v>13.09433859941911</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>427880.7490573229</v>
+        <v>424873.8350814602</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>648071.4658795753</v>
+        <v>642489.5263081721</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>196554.3811374283</v>
+        <v>194175.7487550053</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>242316.8820399614</v>
+        <v>238218.8528266675</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>299270.5413708418</v>
+        <v>292736.9128024795</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>16.7304318487854</v>
+        <v>16.60130268847874</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>22.40698388444868</v>
+        <v>22.19764546606966</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>7.114413292921735</v>
+        <v>7.001126138581915</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>7.849840161893622</v>
+        <v>7.679685386838966</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>8.65346809697478</v>
+        <v>8.417069073570341</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.8911150241738042</v>
+        <v>0.8842372020202436</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>1.304033045602067</v>
+        <v>1.291850048698598</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.4525034045476991</v>
+        <v>0.4452979160668301</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.5519579663990363</v>
+        <v>0.5399936102242223</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.6648615096934321</v>
+        <v>0.6466985477654075</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>456303.1973888405</v>
+        <v>452781.3487446083</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>685300.2718066686</v>
+        <v>678897.8181897723</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>241911.757217158</v>
+        <v>238059.6483435081</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>297445.5769300712</v>
+        <v>290998.0844729343</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>362414.1929362561</v>
+        <v>352513.611999465</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>14.7805191217649</v>
+        <v>14.66643981763573</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>19.74986108172646</v>
+        <v>19.56534697204642</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>6.251269613276644</v>
+        <v>6.151726823683063</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>6.87425453614764</v>
+        <v>6.725246758900811</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>7.53547635736232</v>
+        <v>7.329619095071094</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.9870065173336431</v>
+        <v>0.9793885835019025</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>1.441765352722668</v>
+        <v>1.428295584539271</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.4992728746432474</v>
+        <v>0.4913226472838573</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.607570534945676</v>
+        <v>0.5944007091184734</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.7301614416757423</v>
+        <v>0.7102145891762148</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>456303.1973888405</v>
+        <v>452781.3487446083</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>685300.2718066686</v>
+        <v>678897.8181897723</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>241911.757217158</v>
+        <v>238059.6483435081</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>297445.5769300712</v>
+        <v>290998.0844729343</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>362414.1929362561</v>
+        <v>352513.611999465</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>441.603906823645</v>
+        <v>449.3053808101308</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>487.9426072806427</v>
+        <v>497.5787734949014</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>526.9971134959333</v>
+        <v>541.1250688725133</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>566.6008940872616</v>
+        <v>585.4035510591796</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>614.1759533263676</v>
+        <v>638.054180229045</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>28.69315702585201</v>
+        <v>29.1935593071955</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>34.32167841478562</v>
+        <v>34.99948230610882</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>40.02802355500148</v>
+        <v>41.10111127429906</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>46.99777900338609</v>
+        <v>48.55740082231419</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>54.57370890498387</v>
+        <v>56.69545170050718</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>7162975.208809354</v>
+        <v>7287895.904446492</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>8771831.127015399</v>
+        <v>8945062.202724088</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>10384397.25912369</v>
+        <v>10662786.45202904</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>12274654.19885356</v>
+        <v>12681988.73495898</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>14428290.81634009</v>
+        <v>14989240.81782494</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>452.8345675076336</v>
+        <v>460.7319017203816</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>500.3517317719664</v>
+        <v>510.2329603857524</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>540.3994536284849</v>
+        <v>554.8867044518245</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>581.0104187459276</v>
+        <v>600.2912559539034</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>629.7953842813299</v>
+        <v>654.2808709023557</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>35.20005930311707</v>
+        <v>35.81394051398682</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>42.05761044332785</v>
+        <v>42.88818788985396</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>48.99243033509123</v>
+        <v>50.30583955847917</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>57.4389430965495</v>
+        <v>59.34505506203396</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>66.61560123075081</v>
+        <v>69.20551448416158</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>7162975.208809354</v>
+        <v>7287895.904446492</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>8771831.127015399</v>
+        <v>8945062.202724088</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>10384397.25912369</v>
+        <v>10662786.45202904</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>12274654.19885356</v>
+        <v>12681988.73495898</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>14428290.81634009</v>
+        <v>14989240.81782494</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>935.936326290573</v>
+        <v>952.067300654153</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1047.380532671491</v>
+        <v>1067.656568953744</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1135.89205270745</v>
+        <v>1165.846329154982</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1225.707677602309</v>
+        <v>1265.891363684818</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1341.536952962204</v>
+        <v>1393.372931800439</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>12.80333067083925</v>
+        <v>13.02399760406781</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>15.95294780200157</v>
+        <v>16.26177781970033</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>19.24707069068693</v>
+        <v>19.75462955149577</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>23.24222907536832</v>
+        <v>24.00420393616821</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>27.93957296870532</v>
+        <v>29.01913705373275</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>3198154.77835288</v>
+        <v>3253275.35791713</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>4085387.609679003</v>
+        <v>4164475.834843582</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>5003346.764027089</v>
+        <v>5135288.555304968</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>6066401.557190973</v>
+        <v>6265282.889403449</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>7327987.279028304</v>
+        <v>7611135.195814214</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1024.649821777192</v>
+        <v>1042.30978383064</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1146.65735904085</v>
+        <v>1168.855276120637</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1243.558516397913</v>
+        <v>1276.352033607649</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1341.887389266933</v>
+        <v>1385.879919128426</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1468.695637884106</v>
+        <v>1525.444932666531</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>13.24869537065294</v>
+        <v>13.47703821767321</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>16.50929549193171</v>
+        <v>16.82889573649138</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>19.92019502107876</v>
+        <v>20.44550464634454</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>24.05777328790984</v>
+        <v>24.8464850071157</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>28.92293877609703</v>
+        <v>30.04049937629286</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>3198154.77835288</v>
+        <v>3253275.35791713</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>4085387.609679003</v>
+        <v>4164475.834843582</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>5003346.764027089</v>
+        <v>5135288.555304968</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>6066401.557190973</v>
+        <v>6265282.889403449</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>7327987.279028304</v>
+        <v>7611135.195814214</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>527.6215812150497</v>
+        <v>536.7898536354739</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>587.6845756083513</v>
+        <v>599.2177200844815</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>638.2408448066839</v>
+        <v>655.2602333279284</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>689.1772242846473</v>
+        <v>711.956183958599</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>751.3955331863489</v>
+        <v>780.5481025081931</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>20.74585281666677</v>
+        <v>21.10634533059922</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>25.12810770546236</v>
+        <v>25.6212397504524</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>29.62703432451742</v>
+        <v>30.41707152129686</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>35.12381320911081</v>
+        <v>36.28473945056666</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>41.3097880924195</v>
+        <v>42.91252115090347</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>10361129.98716223</v>
+        <v>10541171.26236362</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>12857218.7366944</v>
+        <v>13109538.03756767</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>15387744.02315078</v>
+        <v>15798075.00733401</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>18341055.75604453</v>
+        <v>18947271.62436243</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>21756278.09536839</v>
+        <v>22600376.01363916</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>547.0703396022129</v>
+        <v>556.5765654375106</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>609.5145033548598</v>
+        <v>621.4760540220888</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>662.135734439431</v>
+        <v>679.7923062648169</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>715.1292396990133</v>
+        <v>738.7659757064695</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>779.8244794264762</v>
+        <v>810.0800321830206</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>23.28934103869398</v>
+        <v>23.69403074574348</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>28.19399348797961</v>
+        <v>28.74729267899435</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>33.22562640486419</v>
+        <v>34.11162398594564</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>39.37041030257176</v>
+        <v>40.67169675985436</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>46.29460857857065</v>
+        <v>48.09074220754141</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>10361129.98716223</v>
+        <v>10541171.26236362</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>12857218.7366944</v>
+        <v>13109538.03756767</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>15387744.02315078</v>
+        <v>15798075.00733401</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>18341055.75604453</v>
+        <v>18947271.62436243</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>21756278.09536839</v>
+        <v>22600376.01363916</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1189.636597559712</v>
+        <v>1196.956591203313</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1325.569639666503</v>
+        <v>1335.138055448614</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1423.025396638752</v>
+        <v>1445.00830415427</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1513.542696414576</v>
+        <v>1548.736733314442</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1605.136437149781</v>
+        <v>1654.319519263379</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>29.91738499317222</v>
+        <v>30.10147067818932</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>37.10612657869268</v>
+        <v>37.37397131241629</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>45.29950640690002</v>
+        <v>45.99929353803181</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>55.23632345587759</v>
+        <v>56.52072013033165</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>67.12063283633506</v>
+        <v>69.17728018412561</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>117352.7667021601</v>
+        <v>118074.8540253653</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>148875.2975974846</v>
+        <v>149949.930498293</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>184011.2768097003</v>
+        <v>186853.8844606071</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>225524.536902599</v>
+        <v>230768.6036159977</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>275838.4966622847</v>
+        <v>284290.4806291569</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1283.433708999925</v>
+        <v>1291.330848858546</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1430.084416253412</v>
+        <v>1440.407255498336</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1535.224089907416</v>
+        <v>1558.940243718688</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1632.878242459757</v>
+        <v>1670.847159527146</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1731.693708152474</v>
+        <v>1784.754639218806</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>30.40789126910184</v>
+        <v>30.59499510506463</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>37.72086549380579</v>
+        <v>37.99314762362027</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>46.06049148887931</v>
+        <v>46.77203432354061</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>56.17979328632273</v>
+        <v>57.48612823321884</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>68.28868638307959</v>
+        <v>70.38112412984995</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>117352.7667021601</v>
+        <v>118074.8540253653</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>148875.2975974846</v>
+        <v>149949.930498293</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>184011.2768097003</v>
+        <v>186853.8844606071</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>225524.536902599</v>
+        <v>230768.6036159977</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>275838.4966622847</v>
+        <v>284290.4806291569</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>530.9305001625936</v>
+        <v>540.0895344169431</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>591.4531952419994</v>
+        <v>602.9763052080251</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>642.427515444439</v>
+        <v>659.4733833595309</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>693.7670975659685</v>
+        <v>716.6151814732502</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>756.4326620933437</v>
+        <v>785.7034127914542</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>20.81732517623008</v>
+        <v>21.17644297849353</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>25.22130055727685</v>
+        <v>25.71267979429116</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>29.74865804459875</v>
+        <v>30.5379948701372</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>35.27985112378941</v>
+        <v>36.44173527992886</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>41.5096332957248</v>
+        <v>43.11588086891489</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>10478482.75386439</v>
+        <v>10659246.11638899</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>13006094.03429189</v>
+        <v>13259487.96806596</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>15571755.29996048</v>
+        <v>15984928.89179461</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>18566580.29294713</v>
+        <v>19178040.22797843</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>22032116.59203068</v>
+        <v>22884666.49426831</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>550.608328295438</v>
+        <v>560.1068229911538</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>613.5442295997166</v>
+        <v>625.4977327400713</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>666.6156392497819</v>
+        <v>684.3033034042745</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>720.0450107092912</v>
+        <v>743.7585146783102</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>785.2282985906941</v>
+        <v>815.6133188587816</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>23.350561628726</v>
+        <v>23.75338006494374</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>28.27573795805519</v>
+        <v>28.82662590740152</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>33.33539426663894</v>
+        <v>34.21989985506089</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>39.51402031964225</v>
+        <v>40.81534990841159</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>46.48203932219572</v>
+        <v>48.2806980173062</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>10478482.75386439</v>
+        <v>10659246.11638899</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>13006094.03429189</v>
+        <v>13259487.96806596</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>15571755.29996048</v>
+        <v>15984928.89179461</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>18566580.29294713</v>
+        <v>19178040.22797843</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>22032116.59203068</v>
+        <v>22884666.49426831</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>970.5424216220612</v>
+        <v>985.3514192188142</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>1025.421756854298</v>
+        <v>1043.250808939713</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>903.2749794753763</v>
+        <v>924.4637706726514</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>944.9704026104795</v>
+        <v>974.8073573912656</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>988.5509880948357</v>
+        <v>1027.301606419323</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>840.4292854282369</v>
+        <v>853.2529549463059</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>895.1622679922247</v>
+        <v>910.7264927555963</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>790.0369290413231</v>
+        <v>808.5694112953048</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>833.0088173479797</v>
+        <v>859.3106426184299</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>880.1024169357399</v>
+        <v>914.6019149442975</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>7315727.696866723</v>
+        <v>7427354.547448209</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>8812640.553662209</v>
+        <v>8965866.313103171</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>8819686.481553895</v>
+        <v>9026576.409349322</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>10517472.50807058</v>
+        <v>10849556.29690097</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>12608434.82853126</v>
+        <v>13102678.07100801</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>617.8200382263489</v>
+        <v>627.2470300378234</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>652.7546812008941</v>
+        <v>664.1041548514546</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>574.9994744337885</v>
+        <v>588.4876636111271</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>601.5416093691581</v>
+        <v>620.5349765137026</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>629.2837856924477</v>
+        <v>653.9513406196368</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>539.3600030310622</v>
+        <v>547.5898143311417</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>574.2400056687868</v>
+        <v>584.2243412869482</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>506.7514914907653</v>
+        <v>518.6387371093055</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>534.0911908470567</v>
+        <v>550.954845693915</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>563.9846142836647</v>
+        <v>586.0924800307906</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>7315727.696866723</v>
+        <v>7427354.547448209</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>8812640.553662209</v>
+        <v>8965866.313103171</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>8819686.481553895</v>
+        <v>9026576.409349322</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>10517472.50807058</v>
+        <v>10849556.29690097</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>12608434.82853126</v>
+        <v>13102678.07100801</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>652.4276554547381</v>
+        <v>663.1481907514795</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>713.3982786880796</v>
+        <v>726.6933571927896</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>717.3309790319877</v>
+        <v>735.5665050653437</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>767.5527338627651</v>
+        <v>792.4536501732922</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>827.1224262791803</v>
+        <v>859.2801942092573</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>34.75033347716098</v>
+        <v>35.32134265112951</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>41.51807913471788</v>
+        <v>42.29182100927908</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>45.62494429757883</v>
+        <v>46.78479223922449</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>53.97012389418047</v>
+        <v>55.72102058058071</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>63.54930287771222</v>
+        <v>66.02004199580483</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>17794210.45073112</v>
+        <v>18086600.66383719</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>21818734.5879541</v>
+        <v>22225354.28116913</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>24391441.78151438</v>
+        <v>25011505.30114394</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>29084052.80101771</v>
+        <v>30027596.5248794</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>34640551.42056194</v>
+        <v>35987344.56527632</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>576.3879572371637</v>
+        <v>585.8590263871539</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>628.8002424909594</v>
+        <v>640.5187296774882</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>630.3020596717505</v>
+        <v>646.3251925824925</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>672.1605476888866</v>
+        <v>693.9667543595433</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>720.2616821398893</v>
+        <v>748.2648014935453</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>38.4897624785032</v>
+        <v>39.12221705605539</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>45.90322937744062</v>
+        <v>46.75869406865784</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>50.34060929919262</v>
+        <v>51.62033583860574</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>59.40788799443787</v>
+        <v>61.33519641491592</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>69.79085107223968</v>
+        <v>72.50425590944103</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>17794210.45073112</v>
+        <v>18086600.66383719</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>21818734.5879541</v>
+        <v>22225354.28116913</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>24391441.78151438</v>
+        <v>25011505.30114394</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>29084052.80101771</v>
+        <v>30027596.5248794</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>34640551.42056194</v>
+        <v>35987344.56527632</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="T91" s="79" t="n">
-        <v>3121.217327502071</v>
+        <v>3121.21732750207</v>
       </c>
       <c r="U91" s="80" t="n">
         <v>3562.8669518995</v>
@@ -10012,7 +10012,7 @@
         <v>500604.5449603763</v>
       </c>
       <c r="K96" s="133" t="n">
-        <v>500999.7904432034</v>
+        <v>500999.7904432033</v>
       </c>
       <c r="L96" s="134" t="n">
         <v>503216.4655729852</v>
@@ -10021,7 +10021,7 @@
         <v>512058.6961395936</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>525523.7005825018</v>
+        <v>525523.7005825017</v>
       </c>
       <c r="O96" s="133" t="n">
         <v>534607.5958455198</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>30871.93309177592</v>
+        <v>30871.93309177591</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>34698.99200661933</v>
@@ -10056,7 +10056,7 @@
         <v>431438.2840905022</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>440621.2607047732</v>
+        <v>440621.2607047731</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>445830.1197158463</v>
